--- a/PAMF_DIG F2 - monthly2026-07-27.xlsx
+++ b/PAMF_DIG F2 - monthly2026-07-27.xlsx
@@ -9831,7 +9831,7 @@
         <v>0.09</v>
       </c>
       <c r="N129" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         <v>0.09</v>
       </c>
       <c r="N203" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O203" t="inlineStr">
         <is>

--- a/PAMF_DIG F2 - monthly2026-07-27.xlsx
+++ b/PAMF_DIG F2 - monthly2026-07-27.xlsx
@@ -4356,7 +4356,7 @@
         <v>0.09</v>
       </c>
       <c r="N54" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>0.09</v>
       </c>
       <c r="N63" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>0.09</v>
       </c>
       <c r="N76" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -7349,7 +7349,7 @@
         <v>0.09</v>
       </c>
       <c r="N95" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>0.09</v>
       </c>
       <c r="N124" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>0.09</v>
       </c>
       <c r="N125" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>0.09</v>
       </c>
       <c r="N130" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>0.09</v>
       </c>
       <c r="N150" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>0.09</v>
       </c>
       <c r="N176" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O176" t="inlineStr">
         <is>
@@ -13846,7 +13846,7 @@
         <v>0.09</v>
       </c>
       <c r="N184" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O184" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>0.09</v>
       </c>
       <c r="N200" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O200" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>0.09</v>
       </c>
       <c r="N256" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O256" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         <v>0.09</v>
       </c>
       <c r="N279" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O279" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>0.09</v>
       </c>
       <c r="N288" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O288" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>0.09</v>
       </c>
       <c r="N295" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O295" t="inlineStr">
         <is>
@@ -22971,7 +22971,7 @@
         <v>0.09</v>
       </c>
       <c r="N309" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O309" t="inlineStr">
         <is>
@@ -23701,7 +23701,7 @@
         <v>0.09</v>
       </c>
       <c r="N319" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O319" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>0.09</v>
       </c>
       <c r="N334" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O334" t="inlineStr">
         <is>
